--- a/RAW_DATA_XLSX/IND_raw_data.xlsx
+++ b/RAW_DATA_XLSX/IND_raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,52 +429,57 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>BX.KLT.DINV.WD.GD.ZS</t>
+          <t>education</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>FP.CPI.TOTL.ZG</t>
+          <t>fdi</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>NE.TRD.GNFS.ZS</t>
+          <t>gdp_growth</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>NV.IND.TOTL.ZS</t>
+          <t>gdp_pc</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>NY.GDP.MKTP.KD.ZG</t>
+          <t>log_gdp_pc</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>NY.GDP.PCAP.KD</t>
+          <t>gini</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>SE.SEC.ENRR</t>
+          <t>industry</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>SI.POV.GINI</t>
+          <t>inflation</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>SL.UEM.TOTL.ZS</t>
+          <t>trade</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>SP.URB.TOTL.IN.ZS</t>
+          <t>unemployment</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>urban</t>
         </is>
       </c>
     </row>
@@ -488,31 +493,34 @@
         <v>1995</v>
       </c>
       <c r="C2" t="n">
+        <v>44.9552116394043</v>
+      </c>
+      <c r="D2" t="n">
         <v>0.594986329567616</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>7.57449183788519</v>
+      </c>
+      <c r="F2" t="n">
+        <v>620.699954330379</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.430847799841997</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>28.5998094242024</v>
+      </c>
+      <c r="J2" t="n">
         <v>10.2248861637544</v>
       </c>
-      <c r="E2" t="n">
+      <c r="K2" t="n">
         <v>22.8674487062499</v>
       </c>
-      <c r="F2" t="n">
-        <v>28.5998094242024</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7.57449183788519</v>
-      </c>
-      <c r="H2" t="n">
-        <v>620.699954330379</v>
-      </c>
-      <c r="I2" t="n">
-        <v>44.9552116394043</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>7.57</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>26.5661772139368</v>
       </c>
     </row>
@@ -526,31 +534,34 @@
         <v>1996</v>
       </c>
       <c r="C3" t="n">
+        <v>44.8827896118164</v>
+      </c>
+      <c r="D3" t="n">
         <v>0.617479351603705</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>7.54952224920051</v>
+      </c>
+      <c r="F3" t="n">
+        <v>654.355928429641</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.483651436488936</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>27.9122703698412</v>
+      </c>
+      <c r="J3" t="n">
         <v>8.97715233826453</v>
       </c>
-      <c r="E3" t="n">
+      <c r="K3" t="n">
         <v>21.9294878713867</v>
       </c>
-      <c r="F3" t="n">
-        <v>27.9122703698412</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7.54952224920051</v>
-      </c>
-      <c r="H3" t="n">
-        <v>654.355928429641</v>
-      </c>
-      <c r="I3" t="n">
-        <v>44.8827896118164</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>7.537</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>26.7648638746349</v>
       </c>
     </row>
@@ -564,31 +575,34 @@
         <v>1997</v>
       </c>
       <c r="C4" t="n">
+        <v>45.3552589416504</v>
+      </c>
+      <c r="D4" t="n">
         <v>0.860208959660141</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>4.04982084998183</v>
+      </c>
+      <c r="F4" t="n">
+        <v>667.598423095039</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.50368682973432</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>27.8370307633106</v>
+      </c>
+      <c r="J4" t="n">
         <v>7.16425211462724</v>
       </c>
-      <c r="E4" t="n">
+      <c r="K4" t="n">
         <v>22.6193868670479</v>
       </c>
-      <c r="F4" t="n">
-        <v>27.8370307633106</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4.04982084998183</v>
-      </c>
-      <c r="H4" t="n">
-        <v>667.598423095039</v>
-      </c>
-      <c r="I4" t="n">
-        <v>45.3552589416504</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>7.574</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>26.9696862023486</v>
       </c>
     </row>
@@ -601,30 +615,33 @@
       <c r="B5" t="n">
         <v>1998</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
         <v>0.625286204187864</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>6.18441582172117</v>
+      </c>
+      <c r="F5" t="n">
+        <v>695.293709344799</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.544334359666948</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>27.3030378517565</v>
+      </c>
+      <c r="J5" t="n">
         <v>13.2308389767977</v>
       </c>
-      <c r="E5" t="n">
+      <c r="K5" t="n">
         <v>23.6994700790647</v>
       </c>
-      <c r="F5" t="n">
-        <v>27.3030378517565</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6.18441582172117</v>
-      </c>
-      <c r="H5" t="n">
-        <v>695.293709344799</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>7.596</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>27.1832515534447</v>
       </c>
     </row>
@@ -638,31 +655,34 @@
         <v>1999</v>
       </c>
       <c r="C6" t="n">
+        <v>42.9011917114258</v>
+      </c>
+      <c r="D6" t="n">
         <v>0.472644191458928</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>8.845755559395309</v>
+      </c>
+      <c r="F6" t="n">
+        <v>742.53920839445</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.610075675201123</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>26.5192933488596</v>
+      </c>
+      <c r="J6" t="n">
         <v>4.66982038037594</v>
       </c>
-      <c r="E6" t="n">
+      <c r="K6" t="n">
         <v>24.8155980442929</v>
       </c>
-      <c r="F6" t="n">
-        <v>26.5192933488596</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8.845755559395309</v>
-      </c>
-      <c r="H6" t="n">
-        <v>742.53920839445</v>
-      </c>
-      <c r="I6" t="n">
-        <v>42.9011917114258</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>7.583</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>27.4081672842903</v>
       </c>
     </row>
@@ -676,31 +696,34 @@
         <v>2000</v>
       </c>
       <c r="C7" t="n">
+        <v>47.1734390258789</v>
+      </c>
+      <c r="D7" t="n">
         <v>0.765211694280817</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>3.84099115659129</v>
+      </c>
+      <c r="F7" t="n">
+        <v>756.704109527449</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.628972304540029</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>27.3258283775917</v>
+      </c>
+      <c r="J7" t="n">
         <v>4.0094359104519</v>
       </c>
-      <c r="E7" t="n">
+      <c r="K7" t="n">
         <v>26.9009229104474</v>
       </c>
-      <c r="F7" t="n">
-        <v>27.3258283775917</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3.84099115659129</v>
-      </c>
-      <c r="H7" t="n">
-        <v>756.704109527449</v>
-      </c>
-      <c r="I7" t="n">
-        <v>47.1734390258789</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>7.589</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>27.6470407512523</v>
       </c>
     </row>
@@ -714,31 +737,34 @@
         <v>2001</v>
       </c>
       <c r="C8" t="n">
+        <v>46.8245811462402</v>
+      </c>
+      <c r="D8" t="n">
         <v>1.05638020993358</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>4.82396626555771</v>
+      </c>
+      <c r="F8" t="n">
+        <v>778.5073775283651</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.657378467823068</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>26.4877773440307</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.77929312235637</v>
       </c>
-      <c r="E8" t="n">
+      <c r="K8" t="n">
         <v>25.9932547534365</v>
       </c>
-      <c r="F8" t="n">
-        <v>26.4877773440307</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4.82396626555771</v>
-      </c>
-      <c r="H8" t="n">
-        <v>778.5073775283651</v>
-      </c>
-      <c r="I8" t="n">
-        <v>46.8245811462402</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>7.611</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>27.9028652096636</v>
       </c>
     </row>
@@ -752,31 +778,34 @@
         <v>2002</v>
       </c>
       <c r="C9" t="n">
+        <v>48.8069381713867</v>
+      </c>
+      <c r="D9" t="n">
         <v>1.01156946489919</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>3.80397532112175</v>
+      </c>
+      <c r="F9" t="n">
+        <v>793.615912906381</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.676599607314973</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>27.6606541607882</v>
+      </c>
+      <c r="J9" t="n">
         <v>4.29715203929563</v>
       </c>
-      <c r="E9" t="n">
+      <c r="K9" t="n">
         <v>29.5086629350614</v>
       </c>
-      <c r="F9" t="n">
-        <v>27.6606541607882</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.80397532112175</v>
-      </c>
-      <c r="H9" t="n">
-        <v>793.615912906381</v>
-      </c>
-      <c r="I9" t="n">
-        <v>48.8069381713867</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>7.681</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>28.1756878910456</v>
       </c>
     </row>
@@ -790,31 +819,34 @@
         <v>2003</v>
       </c>
       <c r="C10" t="n">
+        <v>51.4255714416504</v>
+      </c>
+      <c r="D10" t="n">
         <v>0.605887857091792</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
+        <v>7.8603814759073</v>
+      </c>
+      <c r="F10" t="n">
+        <v>841.278894571674</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6.734923227556812</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>27.4741071211988</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.80585899528851</v>
       </c>
-      <c r="E10" t="n">
+      <c r="K10" t="n">
         <v>30.592436132908</v>
       </c>
-      <c r="F10" t="n">
-        <v>27.4741071211988</v>
-      </c>
-      <c r="G10" t="n">
-        <v>7.8603814759073</v>
-      </c>
-      <c r="H10" t="n">
-        <v>841.278894571674</v>
-      </c>
-      <c r="I10" t="n">
-        <v>51.4255714416504</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>7.633</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>28.4660287698</v>
       </c>
     </row>
@@ -828,33 +860,36 @@
         <v>2004</v>
       </c>
       <c r="C11" t="n">
+        <v>53.247371673584</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.765596855110284</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
+        <v>7.92293661199932</v>
+      </c>
+      <c r="F11" t="n">
+        <v>892.596614581612</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.794134759427068</v>
+      </c>
+      <c r="H11" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>29.219106305293</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.76725173477515</v>
       </c>
-      <c r="E11" t="n">
+      <c r="K11" t="n">
         <v>37.503814059447</v>
       </c>
-      <c r="F11" t="n">
-        <v>29.219106305293</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7.92293661199932</v>
-      </c>
-      <c r="H11" t="n">
-        <v>892.596614581612</v>
-      </c>
-      <c r="I11" t="n">
-        <v>53.247371673584</v>
-      </c>
-      <c r="J11" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7.598</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>28.7726067228528</v>
       </c>
     </row>
@@ -868,31 +903,34 @@
         <v>2005</v>
       </c>
       <c r="C12" t="n">
+        <v>55.9314002990723</v>
+      </c>
+      <c r="D12" t="n">
         <v>0.886098378458823</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
+        <v>7.92343062148318</v>
+      </c>
+      <c r="F12" t="n">
+        <v>947.732565646672</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.854072358708038</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>29.5337641914637</v>
+      </c>
+      <c r="J12" t="n">
         <v>4.24634362031922</v>
       </c>
-      <c r="E12" t="n">
+      <c r="K12" t="n">
         <v>42.0016696148691</v>
       </c>
-      <c r="F12" t="n">
-        <v>29.5337641914637</v>
-      </c>
-      <c r="G12" t="n">
-        <v>7.92343062148318</v>
-      </c>
-      <c r="H12" t="n">
-        <v>947.732565646672</v>
-      </c>
-      <c r="I12" t="n">
-        <v>55.9314002990723</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>7.551</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>29.0945497159107</v>
       </c>
     </row>
@@ -906,31 +944,34 @@
         <v>2006</v>
       </c>
       <c r="C13" t="n">
+        <v>56.7859497070312</v>
+      </c>
+      <c r="D13" t="n">
         <v>2.13016842534495</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
+        <v>8.060732571666509</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1008.23275343783</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6.915954328164906</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>30.9272399435883</v>
+      </c>
+      <c r="J13" t="n">
         <v>5.79652337561634</v>
       </c>
-      <c r="E13" t="n">
+      <c r="K13" t="n">
         <v>45.7244804992652</v>
       </c>
-      <c r="F13" t="n">
-        <v>30.9272399435883</v>
-      </c>
-      <c r="G13" t="n">
-        <v>8.060732571666509</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1008.23275343783</v>
-      </c>
-      <c r="I13" t="n">
-        <v>56.7859497070312</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>7.553</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>29.4309857146804</v>
       </c>
     </row>
@@ -944,31 +985,34 @@
         <v>2007</v>
       </c>
       <c r="C14" t="n">
+        <v>59.1478385925293</v>
+      </c>
+      <c r="D14" t="n">
         <v>2.07339404668754</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
+        <v>7.6608150670107</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1069.24696813025</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6.97470991159236</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>30.9032382510869</v>
+      </c>
+      <c r="J14" t="n">
         <v>6.37288135593231</v>
       </c>
-      <c r="E14" t="n">
+      <c r="K14" t="n">
         <v>45.686268679348</v>
       </c>
-      <c r="F14" t="n">
-        <v>30.9032382510869</v>
-      </c>
-      <c r="G14" t="n">
-        <v>7.6608150670107</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1069.24696813025</v>
-      </c>
-      <c r="I14" t="n">
-        <v>59.1478385925293</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>7.562</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>29.7810426848684</v>
       </c>
     </row>
@@ -982,31 +1026,34 @@
         <v>2008</v>
       </c>
       <c r="C15" t="n">
+        <v>62.2119216918945</v>
+      </c>
+      <c r="D15" t="n">
         <v>3.6205232354017</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>3.08669805921981</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1086.50605251513</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6.990722370334562</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>31.1367192409548</v>
+      </c>
+      <c r="J15" t="n">
         <v>8.349267049075809</v>
       </c>
-      <c r="E15" t="n">
+      <c r="K15" t="n">
         <v>53.3682204392226</v>
       </c>
-      <c r="F15" t="n">
-        <v>31.1367192409548</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3.08669805921981</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1086.50605251513</v>
-      </c>
-      <c r="I15" t="n">
-        <v>62.2119216918945</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>7.629</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>30.1438485921815</v>
       </c>
     </row>
@@ -1020,33 +1067,36 @@
         <v>2009</v>
       </c>
       <c r="C16" t="n">
+        <v>61.3603210449219</v>
+      </c>
+      <c r="D16" t="n">
         <v>2.65159033235479</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
+        <v>7.86188883286074</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1155.10163274172</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7.051943612800449</v>
+      </c>
+      <c r="H16" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>31.1213721116744</v>
+      </c>
+      <c r="J16" t="n">
         <v>10.8823529411764</v>
       </c>
-      <c r="E16" t="n">
+      <c r="K16" t="n">
         <v>46.2728696428837</v>
       </c>
-      <c r="F16" t="n">
-        <v>31.1213721116744</v>
-      </c>
-      <c r="G16" t="n">
-        <v>7.86188883286074</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1155.10163274172</v>
-      </c>
-      <c r="I16" t="n">
-        <v>61.3603210449219</v>
-      </c>
-      <c r="J16" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>7.636</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>30.5185314023263</v>
       </c>
     </row>
@@ -1060,31 +1110,34 @@
         <v>2010</v>
       </c>
       <c r="C17" t="n">
+        <v>64.9475936889648</v>
+      </c>
+      <c r="D17" t="n">
         <v>1.6350340943491</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
+        <v>8.49758470221235</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1235.15939133951</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7.118955302547687</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>30.7250782285817</v>
+      </c>
+      <c r="J17" t="n">
         <v>11.9893899204244</v>
       </c>
-      <c r="E17" t="n">
+      <c r="K17" t="n">
         <v>49.2552064974161</v>
       </c>
-      <c r="F17" t="n">
-        <v>30.7250782285817</v>
-      </c>
-      <c r="G17" t="n">
-        <v>8.49758470221235</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1235.15939133951</v>
-      </c>
-      <c r="I17" t="n">
-        <v>64.9475936889648</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>7.631</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>30.9042190810094</v>
       </c>
     </row>
@@ -1098,33 +1151,36 @@
         <v>2011</v>
       </c>
       <c r="C18" t="n">
+        <v>67.1251678466797</v>
+      </c>
+      <c r="D18" t="n">
         <v>2.0020634629993</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
+        <v>5.24131619937695</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1281.61054354933</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7.155872803144588</v>
+      </c>
+      <c r="H18" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>30.1616797630407</v>
+      </c>
+      <c r="J18" t="n">
         <v>8.911793364833709</v>
       </c>
-      <c r="E18" t="n">
+      <c r="K18" t="n">
         <v>55.6238800135298</v>
       </c>
-      <c r="F18" t="n">
-        <v>30.1616797630407</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5.24131619937695</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1281.61054354933</v>
-      </c>
-      <c r="I18" t="n">
-        <v>67.1251678466797</v>
-      </c>
-      <c r="J18" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>7.609</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>31.2746502853309</v>
       </c>
     </row>
@@ -1138,31 +1194,34 @@
         <v>2012</v>
       </c>
       <c r="C19" t="n">
+        <v>69.8089599609375</v>
+      </c>
+      <c r="D19" t="n">
         <v>1.31293453035323</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
+        <v>5.45638755166587</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1333.09626557668</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.195259534807989</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>29.3985276965289</v>
+      </c>
+      <c r="J19" t="n">
         <v>9.47899691419801</v>
       </c>
-      <c r="E19" t="n">
+      <c r="K19" t="n">
         <v>55.7937217287511</v>
       </c>
-      <c r="F19" t="n">
-        <v>29.3985276965289</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5.45638755166587</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1333.09626557668</v>
-      </c>
-      <c r="I19" t="n">
-        <v>69.8089599609375</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>7.645</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>31.5898935604399</v>
       </c>
     </row>
@@ -1176,31 +1235,34 @@
         <v>2013</v>
       </c>
       <c r="C20" t="n">
+        <v>69.4771270751953</v>
+      </c>
+      <c r="D20" t="n">
         <v>1.5162764665975</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
+        <v>6.38610640094825</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1399.4537980287</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7.243837295212061</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>28.4048995600246</v>
+      </c>
+      <c r="J20" t="n">
         <v>10.0178784746102</v>
       </c>
-      <c r="E20" t="n">
+      <c r="K20" t="n">
         <v>53.8441319466777</v>
       </c>
-      <c r="F20" t="n">
-        <v>28.4048995600246</v>
-      </c>
-      <c r="G20" t="n">
-        <v>6.38610640094825</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1399.4537980287</v>
-      </c>
-      <c r="I20" t="n">
-        <v>69.4771270751953</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>7.678</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>31.9096789235237</v>
       </c>
     </row>
@@ -1214,31 +1276,34 @@
         <v>2014</v>
       </c>
       <c r="C21" t="n">
+        <v>74.8887023925781</v>
+      </c>
+      <c r="D21" t="n">
         <v>1.69565958990806</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>7.41022760508854</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1484.31640682913</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7.302709613149855</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>27.6564012026443</v>
+      </c>
+      <c r="J21" t="n">
         <v>6.66565671867899</v>
       </c>
-      <c r="E21" t="n">
+      <c r="K21" t="n">
         <v>48.9221857470669</v>
       </c>
-      <c r="F21" t="n">
-        <v>27.6564012026443</v>
-      </c>
-      <c r="G21" t="n">
-        <v>7.41022760508854</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1484.31640682913</v>
-      </c>
-      <c r="I21" t="n">
-        <v>74.8887023925781</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>7.656</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>32.2288233408821</v>
       </c>
     </row>
@@ -1252,31 +1317,34 @@
         <v>2015</v>
       </c>
       <c r="C22" t="n">
+        <v>74.6113662719727</v>
+      </c>
+      <c r="D22" t="n">
         <v>2.09211521443253</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
+        <v>7.99625378571471</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1583.99815907985</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7.367707410176632</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>27.34739147794</v>
+      </c>
+      <c r="J22" t="n">
         <v>4.90697344127256</v>
       </c>
-      <c r="E22" t="n">
+      <c r="K22" t="n">
         <v>41.9229138658647</v>
       </c>
-      <c r="F22" t="n">
-        <v>27.34739147794</v>
-      </c>
-      <c r="G22" t="n">
-        <v>7.99625378571471</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1583.99815907985</v>
-      </c>
-      <c r="I22" t="n">
-        <v>74.6113662719727</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>7.629</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>32.5472990022299</v>
       </c>
     </row>
@@ -1290,31 +1358,34 @@
         <v>2016</v>
       </c>
       <c r="C23" t="n">
+        <v>75.9372863769531</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.9373641224439</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
+        <v>8.256305501790861</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1694.46534973825</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7.435122542173674</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>26.6189999399789</v>
+      </c>
+      <c r="J23" t="n">
         <v>4.94821634062141</v>
       </c>
-      <c r="E23" t="n">
+      <c r="K23" t="n">
         <v>40.082485713276</v>
       </c>
-      <c r="F23" t="n">
-        <v>26.6189999399789</v>
-      </c>
-      <c r="G23" t="n">
-        <v>8.256305501790861</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1694.46534973825</v>
-      </c>
-      <c r="I23" t="n">
-        <v>75.9372863769531</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7.611</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>32.8650780972823</v>
       </c>
     </row>
@@ -1328,31 +1399,34 @@
         <v>2017</v>
       </c>
       <c r="C24" t="n">
+        <v>74.67437744140619</v>
+      </c>
+      <c r="D24" t="n">
         <v>1.50731583255894</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
+        <v>6.79538341897911</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1788.69770318446</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7.489243093928637</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>26.5000166464804</v>
+      </c>
+      <c r="J24" t="n">
         <v>3.32817337461298</v>
       </c>
-      <c r="E24" t="n">
+      <c r="K24" t="n">
         <v>40.7424969545225</v>
       </c>
-      <c r="F24" t="n">
-        <v>26.5000166464804</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6.79538341897911</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1788.69770318446</v>
-      </c>
-      <c r="I24" t="n">
-        <v>74.67437744140619</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>7.626</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>33.1821328157539</v>
       </c>
     </row>
@@ -1366,31 +1440,34 @@
         <v>2018</v>
       </c>
       <c r="C25" t="n">
+        <v>76.00257873535161</v>
+      </c>
+      <c r="D25" t="n">
         <v>1.55821483801456</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
+        <v>6.45385134497769</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1883.35772705062</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7.540811487804754</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>26.4120919013735</v>
+      </c>
+      <c r="J25" t="n">
         <v>3.9388264669163</v>
       </c>
-      <c r="E25" t="n">
+      <c r="K25" t="n">
         <v>43.6169693323889</v>
       </c>
-      <c r="F25" t="n">
-        <v>26.4120919013735</v>
-      </c>
-      <c r="G25" t="n">
-        <v>6.45385134497769</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1883.35772705062</v>
-      </c>
-      <c r="I25" t="n">
-        <v>76.00257873535161</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>7.652</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>33.4984353473598</v>
       </c>
     </row>
@@ -1404,31 +1481,34 @@
         <v>2019</v>
       </c>
       <c r="C26" t="n">
+        <v>75.8716506958008</v>
+      </c>
+      <c r="D26" t="n">
         <v>1.78482633957161</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
+        <v>3.87143694070356</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1936.03067741067</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7.568395113480953</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>24.5914753075066</v>
+      </c>
+      <c r="J26" t="n">
         <v>3.72950573539129</v>
       </c>
-      <c r="E26" t="n">
+      <c r="K26" t="n">
         <v>39.9054035306442</v>
       </c>
-      <c r="F26" t="n">
-        <v>24.5914753075066</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3.87143694070356</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1936.03067741067</v>
-      </c>
-      <c r="I26" t="n">
-        <v>75.8716506958008</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>6.51</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>33.8139578818147</v>
       </c>
     </row>
@@ -1442,31 +1522,34 @@
         <v>2020</v>
       </c>
       <c r="C27" t="n">
+        <v>77.62715484123861</v>
+      </c>
+      <c r="D27" t="n">
         <v>2.40620322673636</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
+        <v>-5.77772470686801</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1806.50110583878</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7.499147162731864</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>25.1229058078344</v>
+      </c>
+      <c r="J27" t="n">
         <v>6.62343677628535</v>
       </c>
-      <c r="E27" t="n">
+      <c r="K27" t="n">
         <v>37.7581053292768</v>
       </c>
-      <c r="F27" t="n">
-        <v>25.1229058078344</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-5.77772470686801</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1806.50110583878</v>
-      </c>
-      <c r="I27" t="n">
-        <v>77.62715484123861</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>7.859</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>34.1286726088333</v>
       </c>
     </row>
@@ -1480,31 +1563,34 @@
         <v>2021</v>
       </c>
       <c r="C28" t="n">
+        <v>80.6246396728944</v>
+      </c>
+      <c r="D28" t="n">
         <v>1.41217101040888</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
+        <v>9.689592491928749</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1965.30943437506</v>
+      </c>
+      <c r="G28" t="n">
+        <v>7.583404984870203</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>26.466523606501</v>
+      </c>
+      <c r="J28" t="n">
         <v>5.13140747176369</v>
       </c>
-      <c r="E28" t="n">
+      <c r="K28" t="n">
         <v>45.4230887840446</v>
       </c>
-      <c r="F28" t="n">
-        <v>26.466523606501</v>
-      </c>
-      <c r="G28" t="n">
-        <v>9.689592491928749</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1965.30943437506</v>
-      </c>
-      <c r="I28" t="n">
-        <v>80.6246396728944</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>6.38</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>34.4425517181304</v>
       </c>
     </row>
@@ -1518,33 +1604,36 @@
         <v>2022</v>
       </c>
       <c r="C29" t="n">
+        <v>81.1778608399708</v>
+      </c>
+      <c r="D29" t="n">
         <v>1.49248825904</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
+        <v>7.60936497768895</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2098.2112447615</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7.648840472524994</v>
+      </c>
+      <c r="H29" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>25.3845195629461</v>
+      </c>
+      <c r="J29" t="n">
         <v>6.69903414079852</v>
       </c>
-      <c r="E29" t="n">
+      <c r="K29" t="n">
         <v>50.0752701498882</v>
       </c>
-      <c r="F29" t="n">
-        <v>25.3845195629461</v>
-      </c>
-      <c r="G29" t="n">
-        <v>7.60936497768895</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2098.2112447615</v>
-      </c>
-      <c r="I29" t="n">
-        <v>81.1778608399708</v>
-      </c>
-      <c r="J29" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4.822</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>34.7555673994206</v>
       </c>
     </row>
@@ -1558,31 +1647,34 @@
         <v>2023</v>
       </c>
       <c r="C30" t="n">
+        <v>78.86395912188389</v>
+      </c>
+      <c r="D30" t="n">
         <v>0.771919134264091</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
+        <v>9.19075493028345</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2270.9051808027</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7.727933789055444</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>25.302936496264</v>
+      </c>
+      <c r="J30" t="n">
         <v>5.64914318907925</v>
       </c>
-      <c r="E30" t="n">
+      <c r="K30" t="n">
         <v>44.9928422877561</v>
       </c>
-      <c r="F30" t="n">
-        <v>25.302936496264</v>
-      </c>
-      <c r="G30" t="n">
-        <v>9.19075493028345</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2270.9051808027</v>
-      </c>
-      <c r="I30" t="n">
-        <v>78.86395912188389</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>4.172</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>35.0676918424186</v>
       </c>
     </row>
@@ -1596,31 +1688,34 @@
         <v>2024</v>
       </c>
       <c r="C31" t="n">
+        <v>78.10580732246061</v>
+      </c>
+      <c r="D31" t="n">
         <v>0.694133152879562</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
+        <v>6.49476552383821</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2396.94999213544</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7.781952371528162</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>24.6285041297852</v>
+      </c>
+      <c r="J31" t="n">
         <v>4.95303550973656</v>
       </c>
-      <c r="E31" t="n">
+      <c r="K31" t="n">
         <v>44.6492935069676</v>
       </c>
-      <c r="F31" t="n">
-        <v>24.6285041297852</v>
-      </c>
-      <c r="G31" t="n">
-        <v>6.49476552383821</v>
-      </c>
-      <c r="H31" t="n">
-        <v>2396.94999213544</v>
-      </c>
-      <c r="I31" t="n">
-        <v>78.10580732246061</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>4.173</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>35.3788972368389</v>
       </c>
     </row>
@@ -1633,20 +1728,21 @@
       <c r="B32" t="n">
         <v>2025</v>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="n">
+        <v>79.59498508646899</v>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="n">
-        <v>79.59498508646899</v>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
         <v>4.219</v>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
